--- a/experiments/results/resnet18/CIFAR-10/ReAct+DICE/standard/results.xlsx
+++ b/experiments/results/resnet18/CIFAR-10/ReAct+DICE/standard/results.xlsx
@@ -353,7 +353,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O3"/>
+  <dimension ref="A1:O5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="61.33203125" customWidth="1" style="3" min="15" max="15"/>
@@ -517,6 +517,104 @@
         <v>96.5</v>
       </c>
       <c r="O3" s="5" t="inlineStr">
+        <is>
+          <t>dice_p=70,ash_p=None,react_th=0.4,scale_th=None,type=avg</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="n">
+        <v>12.25</v>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>97.84999999999999</v>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>45.8</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>91.26000000000001</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>17.54</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>96.97</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>26.99</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>99.65000000000001</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>97.15000000000001</v>
+      </c>
+      <c r="M4" s="5" t="n">
+        <v>20.05</v>
+      </c>
+      <c r="N4" s="5" t="n">
+        <v>96.41</v>
+      </c>
+      <c r="O4" s="5" t="inlineStr">
+        <is>
+          <t>dice_p=70,ash_p=None,react_th=0.5,scale_th=None,type=avg</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="n">
+        <v>11.05</v>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>98.06999999999999</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>47.53</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>91.14</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>17.19</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>97.04000000000001</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>24.33</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>95.91</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>99.66</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>16.24</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>97.19</v>
+      </c>
+      <c r="M5" s="5" t="n">
+        <v>19.65</v>
+      </c>
+      <c r="N5" s="5" t="n">
+        <v>96.5</v>
+      </c>
+      <c r="O5" s="5" t="inlineStr">
         <is>
           <t>dice_p=70,ash_p=None,react_th=0.4,scale_th=None,type=avg</t>
         </is>
